--- a/XBRL-template-MFRS/Company/06-SOCI-NetOfTax.xlsx
+++ b/XBRL-template-MFRS/Company/06-SOCI-NetOfTax.xlsx
@@ -727,8 +727,14 @@
           <t>Other comprehensive income, net of tax, gains (losses) on other items</t>
         </is>
       </c>
-      <c r="B13" s="27" t="n"/>
-      <c r="C13" s="27" t="n"/>
+      <c r="B13" s="27">
+        <f>1*B10+1*B11+1*B12</f>
+        <v/>
+      </c>
+      <c r="C13" s="27">
+        <f>1*C10+1*C11+1*C12</f>
+        <v/>
+      </c>
       <c r="D13" s="32" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1" s="10">
@@ -748,11 +754,11 @@
         </is>
       </c>
       <c r="B15" s="36">
-        <f>1*B12+1*B13+1*B14</f>
+        <f>1*B13+1*B14</f>
         <v/>
       </c>
       <c r="C15" s="36">
-        <f>1*C12+1*C13+1*C14</f>
+        <f>1*C13+1*C14</f>
         <v/>
       </c>
       <c r="D15" s="37" t="n"/>
@@ -804,11 +810,11 @@
         </is>
       </c>
       <c r="B20" s="36">
-        <f>1*B18+1*B19</f>
+        <f>1*B18+-1*B19</f>
         <v/>
       </c>
       <c r="C20" s="36">
-        <f>1*C18+1*C19</f>
+        <f>1*C18+-1*C19</f>
         <v/>
       </c>
       <c r="D20" s="37" t="n"/>
@@ -850,11 +856,11 @@
         </is>
       </c>
       <c r="B24" s="36">
-        <f>1*B22+1*B23</f>
+        <f>1*B22+-1*B23</f>
         <v/>
       </c>
       <c r="C24" s="36">
-        <f>1*C22+1*C23</f>
+        <f>1*C22+-1*C23</f>
         <v/>
       </c>
       <c r="D24" s="37" t="n"/>
@@ -895,8 +901,14 @@
           <t>Other comprehensive income, net of tax, exchange differences on translation of foreign operations</t>
         </is>
       </c>
-      <c r="B28" s="34" t="n"/>
-      <c r="C28" s="34" t="n"/>
+      <c r="B28" s="34">
+        <f>1*B26+-1*B27</f>
+        <v/>
+      </c>
+      <c r="C28" s="34">
+        <f>1*C26+-1*C27</f>
+        <v/>
+      </c>
       <c r="D28" s="35" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1" s="10">
@@ -946,11 +958,11 @@
         </is>
       </c>
       <c r="B33" s="29">
-        <f>1*B26+1*B27+1*B28+1*B30+1*B31+1*B32</f>
+        <f>1*B30+-1*B31+-1*B32</f>
         <v/>
       </c>
       <c r="C33" s="29">
-        <f>1*C26+1*C27+1*C28+1*C30+1*C31+1*C32</f>
+        <f>1*C30+-1*C31+-1*C32</f>
         <v/>
       </c>
       <c r="D33" s="33" t="n"/>
@@ -982,11 +994,11 @@
         </is>
       </c>
       <c r="B36" s="29">
-        <f>1*B34+1*B35</f>
+        <f>1*B20+1*B24+1*B28+1*B33+1*B34+1*B35</f>
         <v/>
       </c>
       <c r="C36" s="29">
-        <f>1*C34+1*C35</f>
+        <f>1*C20+1*C24+1*C28+1*C33+1*C34+1*C35</f>
         <v/>
       </c>
       <c r="D36" s="33" t="n"/>
@@ -998,11 +1010,11 @@
         </is>
       </c>
       <c r="B37" s="29">
-        <f>1*B11+1*B15+1*B36</f>
+        <f>1*B15+1*B36</f>
         <v/>
       </c>
       <c r="C37" s="29">
-        <f>1*C11+1*C15+1*C36</f>
+        <f>1*C15+1*C36</f>
         <v/>
       </c>
       <c r="D37" s="33" t="n"/>
